--- a/georgia_ev_intelligence/outputs/Normalized_kb.xlsx
+++ b/georgia_ev_intelligence/outputs/Normalized_kb.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalized_kb" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="missing_summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="category_values" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="primary_facility_type_values" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="supplier_or_affiliation_type_va" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ev_battery_relevant_values" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ev_supply_chain_role_values" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Normalized_kb" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="missing_summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="category_values" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="primary_facility_type_values" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="supplier_or_affiliation_type_va" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ev_battery_relevant_values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ev_supply_chain_role_values" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,82 +423,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>company</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>industry_group</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>updated_location</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>address</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>primary_facility_type</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ev_supply_chain_role</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>primary_oems</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>supplier_or_affiliation_type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>employment</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>product_service</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ev_battery_relevant</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>classification_method</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>_row_id</t>
         </is>
@@ -13778,7 +13766,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>OEM (Footprint)</t>
+          <t>OEM Footprint</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -13878,7 +13866,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Manufacturing / OEM operations</t>
+          <t>Manufacturing/ OEM operations</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13926,7 +13914,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>OEM (Footprint)</t>
+          <t>OEM Footprint</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -14000,7 +13988,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>OEM (Footprint)</t>
+          <t>OEM Footprint</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -14074,7 +14062,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>OEM (Footprint)</t>
+          <t>OEM Footprint</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -14148,7 +14136,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>OEM (Footprint)</t>
+          <t>OEM Footprint</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -14248,7 +14236,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing Plant</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14326,7 +14314,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing Plant</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14400,7 +14388,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing Plant</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14474,7 +14462,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing Plant</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14548,7 +14536,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing Plant</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14622,7 +14610,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing Plant</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14696,7 +14684,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing Plant</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14770,7 +14758,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing Plant</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14844,7 +14832,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing Plant</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14918,7 +14906,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing Plant</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -14992,7 +14980,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Manufacturing / Engineering</t>
+          <t>Manufacturing/ Engineering</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -15140,7 +15128,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Manufacturing / Engineering</t>
+          <t>Manufacturing/ Engineering</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -15288,7 +15276,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Engineering / Manufacturing</t>
+          <t>Engineering/ Manufacturing</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -15362,7 +15350,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Engineering / Operations</t>
+          <t>Engineering/ Operations</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15436,7 +15424,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Engineering / Operations</t>
+          <t>Engineering/ Operations</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -15719,17 +15707,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>column</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>unknown_count</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>unknown_percent</t>
         </is>
@@ -15954,16 +15942,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -16022,21 +16010,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OEM (Footprint)</t>
+          <t>OEM Footprint</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OEM Footprint</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -16050,16 +16028,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>primary_facility_type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -16072,33 +16050,33 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Manufacturing plant</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>North American Headquarters</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>North American Headquarters</t>
+          <t>Corporate operations</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -16108,7 +16086,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Corporate operations</t>
+          <t>Manufacturing/ Engineering</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -16118,7 +16096,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Manufacturing / Engineering</t>
+          <t>Engineering/ Operations</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -16128,17 +16106,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineering / Operations</t>
+          <t>Headquarters</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Headquarters</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -16148,7 +16126,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>Manufacturing/ OEM operations</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -16158,7 +16136,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manufacturing / OEM operations</t>
+          <t>Regional corporate operations</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -16168,7 +16146,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regional corporate operations</t>
+          <t>Engineering/ Manufacturing</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -16178,20 +16156,10 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineering / Manufacturing</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16210,12 +16178,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>supplier_or_affiliation_type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -16266,12 +16234,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ev_battery_relevant</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -16332,12 +16300,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ev_supply_chain_role</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -16406,7 +16374,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>High‑voltage EV connectors and electronics</t>
+          <t>Power Electronics</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -16416,7 +16384,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Interior and exterior plastic parts</t>
+          <t>Charging Infrastructure</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -16426,7 +16394,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Interior trim and textile components</t>
+          <t>OEM corporate footprint influencing EV strategy</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -16436,7 +16404,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HV and LV wiring harnesses for EVs and ICE vehicles</t>
+          <t>Vehicle safety systems OEM (EV + ICE)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -16446,7 +16414,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EV wiring harnesses and power distribution</t>
+          <t>OEM corporate and engineering footprint (electrification)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -16456,7 +16424,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Power electronics, sensors, and EV systems</t>
+          <t>OEM parent group footprint (EV + HD electrification)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -16466,7 +16434,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EV electrical distribution and interior systems</t>
+          <t>OEM parent group footprint (electric truck strategy)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -16476,7 +16444,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Advanced electrical architecture for EVs</t>
+          <t>OEM corporate footprint and supplier integration</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -16486,7 +16454,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Plastic components for EV and ICE vehicles</t>
+          <t>Machined components supporting EV and ICE vehicles</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -16496,7 +16464,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EV sensors, braking, and control systems</t>
+          <t>Tier 1 automotive components</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -16506,7 +16474,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EV body, powertrain, and thermal components</t>
+          <t>Body and chassis components for EV and ICE OEMs</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -16516,7 +16484,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EV thermal management and power electronics</t>
+          <t>Stamped and welded assemblies for OEMs</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -16526,7 +16494,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stamped metal components for OEMs</t>
+          <t>EV and ICE component manufacturing</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -16536,7 +16504,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stamped and welded assemblies for OEMs</t>
+          <t>EV and ICE powertrain and HVAC components</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -16546,7 +16514,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EV and ICE powertrain and HVAC components</t>
+          <t>Plastic components for EV and ICE vehicles</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -16556,7 +16524,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EV and ICE component manufacturing</t>
+          <t>Stamped metal components for OEMs</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -16566,7 +16534,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Body and chassis components for EV and ICE OEMs</t>
+          <t>Interior and exterior plastic parts</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -16576,7 +16544,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tier 1 automotive components</t>
+          <t>Interior trim and textile components</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -16586,7 +16554,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Machined components supporting EV and ICE vehicles</t>
+          <t>HV and LV wiring harnesses for EVs and ICE vehicles</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -16596,7 +16564,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OEM corporate footprint and supplier integration</t>
+          <t>EV wiring harnesses and power distribution</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -16606,7 +16574,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OEM parent group footprint (electric truck strategy)</t>
+          <t>High‑voltage EV connectors and electronics</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -16616,7 +16584,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>OEM parent group footprint (EV + HD electrification)</t>
+          <t>EV electrical distribution and interior systems</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -16626,7 +16594,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OEM corporate and engineering footprint (electrification)</t>
+          <t>Advanced electrical architecture for EVs</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -16636,7 +16604,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vehicle safety systems OEM (EV + ICE)</t>
+          <t>Power electronics, sensors, and EV systems</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -16646,7 +16614,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OEM corporate footprint influencing EV strategy</t>
+          <t>EV sensors, braking, and control systems</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -16656,7 +16624,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Charging Infrastructure</t>
+          <t>EV body, powertrain, and thermal components</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -16666,7 +16634,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Power Electronics</t>
+          <t>EV thermal management and power electronics</t>
         </is>
       </c>
       <c r="B34" t="n">
